--- a/Unity/Assets/Config/Excel/SceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SceneConfig.xlsx
@@ -468,7 +468,7 @@
     <t>天空之城</t>
   </si>
   <si>
-    <t>-1733,0,163</t>
+    <t>-33,0,163</t>
   </si>
   <si>
     <t>1001,1002,1003,1004,1005,1006,1007,1008,1009,1010</t>
